--- a/xlsx/Power/p3.xlsx
+++ b/xlsx/Power/p3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F0C5E3-75CD-4EB1-A6D7-7F9F11B06276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D30010-9B7B-4F11-B070-5AA49BF85104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="C1">
-        <v>0.14000000000000001</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D1">
-        <v>0.191</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="E1">
-        <v>0.192</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="F1">
-        <v>0.214</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="G1">
-        <v>0.249</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="H1">
-        <v>0.25</v>
+        <v>0.151</v>
       </c>
       <c r="I1">
-        <v>0.29199999999999998</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="J1">
-        <v>0.28799999999999998</v>
+        <v>0.20200000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.124</v>
       </c>
       <c r="C2">
-        <v>0.17399999999999999</v>
+        <v>1.9E-2</v>
       </c>
       <c r="D2">
-        <v>0.23599999999999999</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="E2">
-        <v>0.24</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F2">
-        <v>0.28100000000000003</v>
+        <v>0.125</v>
       </c>
       <c r="G2">
-        <v>0.31900000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="H2">
-        <v>0.308</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I2">
-        <v>0.35099999999999998</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J2">
-        <v>0.34200000000000003</v>
+        <v>0.26400000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="C3">
-        <v>0.111</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="D3">
-        <v>0.16500000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="E3">
-        <v>0.158</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F3">
-        <v>0.157</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G3">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="H3">
-        <v>0.20699999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="I3">
-        <v>0.22</v>
+        <v>0.221</v>
       </c>
       <c r="J3">
-        <v>0.24</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.08</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="B4">
-        <v>8.8999999999999996E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="C4">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="D4">
-        <v>0.14499999999999999</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="E4">
-        <v>0.13600000000000001</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="F4">
-        <v>0.13900000000000001</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="G4">
         <v>0.16900000000000001</v>
       </c>
       <c r="H4">
-        <v>0.17399999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="I4">
-        <v>0.19500000000000001</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="J4">
-        <v>0.21</v>
+        <v>0.21299999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.23699999999999999</v>
       </c>
       <c r="C5">
-        <v>0.34</v>
+        <v>1E-3</v>
       </c>
       <c r="D5">
-        <v>0.432</v>
+        <v>0.04</v>
       </c>
       <c r="E5">
-        <v>0.505</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="F5">
-        <v>0.57899999999999996</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="G5">
-        <v>0.68200000000000005</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="H5">
-        <v>0.76700000000000002</v>
+        <v>0.501</v>
       </c>
       <c r="I5">
-        <v>0.84299999999999997</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="J5">
-        <v>0.873</v>
+        <v>0.70599999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="C6">
-        <v>0.183</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="D6">
-        <v>0.248</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E6">
-        <v>0.26</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="F6">
-        <v>0.3</v>
+        <v>0.314</v>
       </c>
       <c r="G6">
-        <v>0.34</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="H6">
-        <v>0.318</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="I6">
-        <v>0.376</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J6">
-        <v>0.374</v>
+        <v>0.38300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.13</v>
       </c>
       <c r="C7">
-        <v>0.17199999999999999</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="D7">
-        <v>0.21</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="E7">
         <v>0.218</v>
       </c>
       <c r="F7">
-        <v>0.24199999999999999</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="G7">
-        <v>0.29899999999999999</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="H7">
         <v>0.253</v>
       </c>
       <c r="I7">
-        <v>0.315</v>
+        <v>0.313</v>
       </c>
       <c r="J7">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="C8">
-        <v>5.8000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>6.5000000000000002E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E8">
-        <v>8.3000000000000004E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="F8">
-        <v>6.7000000000000004E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G8">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H8">
-        <v>9.9000000000000005E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I8">
-        <v>0.11700000000000001</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="J8">
-        <v>0.114</v>
+        <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="C9">
-        <v>0.154</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="D9">
+        <v>0.79</v>
+      </c>
+      <c r="E9">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="F9">
+        <v>0.127</v>
+      </c>
+      <c r="G9">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="E9">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="F9">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="G9">
-        <v>5.6000000000000001E-2</v>
-      </c>
       <c r="H9">
-        <v>4.5999999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="I9">
-        <v>0.05</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="J9">
-        <v>5.6000000000000001E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p3.xlsx
+++ b/xlsx/Power/p3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D30010-9B7B-4F11-B070-5AA49BF85104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A18166-3D0D-4474-B9F9-4B65D3B96FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="C1">
-        <v>1.4999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D1">
-        <v>3.4000000000000002E-2</v>
+        <v>0.191</v>
       </c>
       <c r="E1">
-        <v>7.1999999999999995E-2</v>
+        <v>0.192</v>
       </c>
       <c r="F1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.214</v>
       </c>
       <c r="G1">
-        <v>0.14899999999999999</v>
+        <v>0.249</v>
       </c>
       <c r="H1">
-        <v>0.151</v>
+        <v>0.25</v>
       </c>
       <c r="I1">
-        <v>0.17799999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="J1">
-        <v>0.20200000000000001</v>
+        <v>0.28799999999999998</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.124</v>
       </c>
       <c r="C2">
-        <v>1.9E-2</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="D2">
-        <v>5.3999999999999999E-2</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="E2">
-        <v>9.6000000000000002E-2</v>
+        <v>0.24</v>
       </c>
       <c r="F2">
-        <v>0.125</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="G2">
-        <v>0.187</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="H2">
-        <v>0.19800000000000001</v>
+        <v>0.308</v>
       </c>
       <c r="I2">
-        <v>0.23899999999999999</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="J2">
-        <v>0.26400000000000001</v>
+        <v>0.34200000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="C3">
-        <v>0.14499999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="D3">
-        <v>0.17199999999999999</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="E3">
-        <v>0.16300000000000001</v>
+        <v>0.158</v>
       </c>
       <c r="F3">
-        <v>0.16200000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="G3">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="H3">
-        <v>0.21</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="I3">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="J3">
-        <v>0.246</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9.0999999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="B4">
-        <v>9.5000000000000001E-2</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="C4">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="D4">
-        <v>0.14299999999999999</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="E4">
-        <v>0.13700000000000001</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="F4">
-        <v>0.14299999999999999</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="G4">
         <v>0.16900000000000001</v>
       </c>
       <c r="H4">
-        <v>0.17199999999999999</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="I4">
-        <v>0.19400000000000001</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="J4">
-        <v>0.21299999999999999</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.23699999999999999</v>
       </c>
       <c r="C5">
-        <v>1E-3</v>
+        <v>0.34</v>
       </c>
       <c r="D5">
-        <v>0.04</v>
+        <v>0.432</v>
       </c>
       <c r="E5">
-        <v>0.13400000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="F5">
-        <v>0.23499999999999999</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="G5">
-        <v>0.38900000000000001</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="H5">
-        <v>0.501</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="I5">
-        <v>0.63300000000000001</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="J5">
-        <v>0.70599999999999996</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="C6">
-        <v>0.30399999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="D6">
-        <v>0.28699999999999998</v>
+        <v>0.248</v>
       </c>
       <c r="E6">
-        <v>0.29099999999999998</v>
+        <v>0.26</v>
       </c>
       <c r="F6">
-        <v>0.314</v>
+        <v>0.3</v>
       </c>
       <c r="G6">
-        <v>0.34799999999999998</v>
+        <v>0.34</v>
       </c>
       <c r="H6">
-        <v>0.32400000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="I6">
-        <v>0.38500000000000001</v>
+        <v>0.376</v>
       </c>
       <c r="J6">
-        <v>0.38300000000000001</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.13</v>
       </c>
       <c r="C7">
-        <v>0.16600000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D7">
-        <v>0.20899999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="E7">
         <v>0.218</v>
       </c>
       <c r="F7">
-        <v>0.24099999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="G7">
-        <v>0.29099999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="H7">
         <v>0.253</v>
       </c>
       <c r="I7">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="J7">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="D8">
-        <v>4.0000000000000001E-3</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="E8">
-        <v>8.9999999999999993E-3</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="F8">
-        <v>1.4E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="G8">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H8">
-        <v>4.4999999999999998E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I8">
-        <v>6.0000000000000001E-3</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="J8">
-        <v>7.0000000000000001E-3</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="C9">
-        <v>0.38400000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="D9">
-        <v>0.79</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E9">
-        <v>0.47399999999999998</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="F9">
-        <v>0.127</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="G9">
-        <v>7.2999999999999995E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="H9">
-        <v>0.06</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="I9">
-        <v>5.8999999999999997E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J9">
-        <v>6.7000000000000004E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p3.xlsx
+++ b/xlsx/Power/p3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A18166-3D0D-4474-B9F9-4B65D3B96FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8BF0ED-8D3C-4DFB-9FFB-27CEDC639605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1AEC95F2-36B8-484A-B946-CDB2AC98DA79}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,42 +398,42 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>7.8E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="B1">
-        <v>9.6000000000000002E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="C1">
         <v>0.14000000000000001</v>
       </c>
       <c r="D1">
-        <v>0.191</v>
+        <v>0.193</v>
       </c>
       <c r="E1">
-        <v>0.192</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="F1">
-        <v>0.214</v>
+        <v>0.215</v>
       </c>
       <c r="G1">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
       <c r="H1">
         <v>0.25</v>
       </c>
       <c r="I1">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="J1">
         <v>0.29199999999999998</v>
-      </c>
-      <c r="J1">
-        <v>0.28799999999999998</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9.4E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="B2">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="C2">
         <v>0.17399999999999999</v>
@@ -442,22 +442,22 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="E2">
-        <v>0.24</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="F2">
-        <v>0.28100000000000003</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="G2">
-        <v>0.31900000000000001</v>
+        <v>0.314</v>
       </c>
       <c r="H2">
-        <v>0.308</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="I2">
-        <v>0.35099999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="J2">
-        <v>0.34200000000000003</v>
+        <v>0.34599999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -465,100 +465,100 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="B3">
-        <v>9.1999999999999998E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="C3">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="D3">
         <v>0.16500000000000001</v>
       </c>
       <c r="E3">
+        <v>0.16</v>
+      </c>
+      <c r="F3">
         <v>0.158</v>
       </c>
-      <c r="F3">
-        <v>0.157</v>
-      </c>
       <c r="G3">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="H3">
-        <v>0.20699999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I3">
-        <v>0.22</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="J3">
-        <v>0.24</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.08</v>
+        <v>7.8E-2</v>
       </c>
       <c r="B4">
-        <v>8.8999999999999996E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="D4">
-        <v>0.14399999999999999</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="E4">
-        <v>0.13600000000000001</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="F4">
-        <v>0.13900000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="G4">
         <v>0.16900000000000001</v>
       </c>
       <c r="H4">
-        <v>0.17399999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="I4">
-        <v>0.19500000000000001</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J4">
-        <v>0.21</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.23699999999999999</v>
+        <v>1E-3</v>
       </c>
       <c r="C5">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.432</v>
+        <v>2E-3</v>
       </c>
       <c r="E5">
-        <v>0.505</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0.57899999999999996</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0.68200000000000005</v>
+        <v>2E-3</v>
       </c>
       <c r="H5">
-        <v>0.76700000000000002</v>
+        <v>2E-3</v>
       </c>
       <c r="I5">
-        <v>0.84299999999999997</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.872</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>9.5000000000000001E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="B6">
         <v>0.14099999999999999</v>
@@ -570,36 +570,36 @@
         <v>0.248</v>
       </c>
       <c r="E6">
-        <v>0.26</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="F6">
-        <v>0.3</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="G6">
-        <v>0.34</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="H6">
-        <v>0.318</v>
+        <v>0.309</v>
       </c>
       <c r="I6">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="J6">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9.7000000000000003E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="B7">
         <v>0.13</v>
       </c>
       <c r="C7">
-        <v>0.17199999999999999</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="D7">
-        <v>0.21</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E7">
         <v>0.218</v>
@@ -631,13 +631,13 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="D8">
-        <v>6.5000000000000002E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E8">
-        <v>8.3000000000000004E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="F8">
-        <v>6.7000000000000004E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="G8">
         <v>0.09</v>
@@ -646,7 +646,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I8">
-        <v>0.11700000000000001</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="J8">
         <v>0.114</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>5.6000000000000001E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="B9">
         <v>7.0999999999999994E-2</v>
@@ -663,13 +663,13 @@
         <v>0.154</v>
       </c>
       <c r="D9">
-        <v>7.2999999999999995E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="E9">
-        <v>7.0999999999999994E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F9">
-        <v>5.1999999999999998E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G9">
         <v>5.6000000000000001E-2</v>
@@ -678,10 +678,10 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="I9">
-        <v>0.05</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J9">
-        <v>5.6000000000000001E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
     </row>
   </sheetData>
